--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513302_ELIMINGRD12FINAL_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513302_ELIMINGRD12FINAL_PROCESSED.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.225099999999999</v>
+        <v>7.2637</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2673</v>
+        <v>4.2615</v>
       </c>
       <c r="F2" t="n">
-        <v>3.9578</v>
+        <v>3.0022</v>
       </c>
       <c r="G2" t="n">
-        <v>1.3357</v>
+        <v>1.3401</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7013</v>
+        <v>1.7781</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3657</v>
+        <v>-0.4381</v>
       </c>
       <c r="J2" t="n">
-        <v>2.1885</v>
+        <v>2.3938</v>
       </c>
       <c r="K2" t="n">
-        <v>2.0666</v>
+        <v>2.2478</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1219</v>
+        <v>0.146</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8529</v>
+        <v>-1.0537</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.3653</v>
+        <v>-0.4696</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.4875</v>
+        <v>-0.5841</v>
       </c>
       <c r="P2" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R2" t="n">
-        <v>3.0009</v>
+        <v>2.921</v>
       </c>
       <c r="S2" t="n">
-        <v>1.69</v>
+        <v>0.6763</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1198</v>
+        <v>-0.4587</v>
       </c>
       <c r="U2" t="n">
-        <v>1.8098</v>
+        <v>1.1349</v>
       </c>
       <c r="V2" t="n">
-        <v>4.1992</v>
+        <v>4.2737</v>
       </c>
       <c r="W2" t="n">
-        <v>4.1992</v>
+        <v>4.2737</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.4616</v>
+        <v>7.0744</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6542</v>
+        <v>6.3295</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8074</v>
+        <v>0.7449</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2103</v>
+        <v>3.276</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.9958</v>
+        <v>-1.9859</v>
       </c>
       <c r="I3" t="n">
-        <v>5.2061</v>
+        <v>5.2619</v>
       </c>
       <c r="J3" t="n">
-        <v>4.0906</v>
+        <v>4.2982</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.3524</v>
+        <v>-1.2622</v>
       </c>
       <c r="L3" t="n">
-        <v>5.443</v>
+        <v>5.5605</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8803</v>
+        <v>-1.0222</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6434</v>
+        <v>-0.7236</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2369</v>
+        <v>-0.2986</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7487</v>
+        <v>-0.2017</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0958</v>
+        <v>-0.6903</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3471</v>
+        <v>0.4887</v>
       </c>
       <c r="V3" t="n">
-        <v>2.3995</v>
+        <v>2.4421</v>
       </c>
       <c r="W3" t="n">
-        <v>2.6593</v>
+        <v>2.7216</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2429</v>
+        <v>2.084</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7848000000000001</v>
+        <v>0.8296</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4581</v>
+        <v>1.2544</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6573</v>
+        <v>2.7066</v>
       </c>
       <c r="H4" t="n">
-        <v>2.0612</v>
+        <v>2.1476</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5961</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4229</v>
+        <v>2.5499</v>
       </c>
       <c r="K4" t="n">
-        <v>2.3829</v>
+        <v>2.5094</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2344</v>
+        <v>0.1567</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3217</v>
+        <v>-0.3618</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5561</v>
+        <v>0.5185</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6453</v>
+        <v>0.4622</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3624</v>
+        <v>0.227</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2829</v>
+        <v>0.2351</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.8597</v>
+        <v>-0.89</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.8597</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0668</v>
+        <v>1.0104</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2689</v>
+        <v>0.2798</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3356</v>
+        <v>0.7307</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.3133</v>
+        <v>-2.3211</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.5203</v>
+        <v>-1.504</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.793</v>
+        <v>-0.8171</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.2903</v>
+        <v>-2.1936</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.9343</v>
+        <v>-0.8646</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.356</v>
+        <v>-1.329</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.023</v>
+        <v>-0.1275</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.586</v>
+        <v>-0.6394</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5119</v>
       </c>
       <c r="P5" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1798</v>
+        <v>0.1631</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6379</v>
+        <v>-0.2483</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8176</v>
+        <v>0.4114</v>
       </c>
       <c r="V5" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="W5" t="n">
-        <v>2.6593</v>
+        <v>2.7216</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="6">
@@ -877,28 +877,28 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. PAREDES BERMEJO</t>
+          <t>A. DIAZ FERREIRA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1705</v>
+        <v>-0.1565</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6935</v>
+        <v>0.7744</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8641</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1131</v>
+        <v>-1.2504</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0713</v>
+        <v>-0.7087</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1844</v>
+        <v>-0.5417999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>0.08</v>
+        <v>0.2494</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.0873</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08</v>
+        <v>0.1621</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1931</v>
+        <v>-1.4999</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0713</v>
+        <v>-0.796</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2643</v>
+        <v>-0.7039</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2001</v>
+        <v>1.3632</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2001</v>
+        <v>1.3632</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9423</v>
+        <v>-0.5487</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6135</v>
+        <v>-0.9755</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3287</v>
+        <v>0.4268</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.1998</v>
+        <v>0.2795</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.5005</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="8">
@@ -1033,22 +1033,22 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2449</v>
+        <v>-0.2313</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2449</v>
+        <v>-0.2313</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2643</v>
+        <v>-0.2776</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3999</v>
+        <v>-0.4105</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1060,13 +1060,13 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2643</v>
+        <v>-0.2776</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3999</v>
+        <v>-0.4105</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0193</v>
+        <v>0.0464</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0193</v>
+        <v>0.0464</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. DIAZ FERREIRA</t>
+          <t>I. VAZQUEZ FLORES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5073</v>
+        <v>-0.3569</v>
       </c>
       <c r="E9" t="n">
-        <v>0.354</v>
+        <v>-1.9592</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8614000000000001</v>
+        <v>1.6023</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.161</v>
+        <v>0.3448</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6842</v>
+        <v>-0.3197</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4769</v>
+        <v>0.6645</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1836</v>
+        <v>0.1026</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0236</v>
+        <v>0.1026</v>
       </c>
       <c r="L9" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3446</v>
+        <v>0.2422</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7078</v>
+        <v>-0.4224</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6369</v>
+        <v>0.6645</v>
       </c>
       <c r="P9" t="n">
-        <v>1.4004</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.9474</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4004</v>
+        <v>1.1684</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0065</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2891</v>
+        <v>-0.1144</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2826</v>
+        <v>0.1917</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2598</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.4596</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. VAZQUEZ FLORES</t>
+          <t>J. PAREDES BERMEJO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5377</v>
+        <v>-0.6216</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0228</v>
+        <v>0.3847</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4851</v>
+        <v>-1.0063</v>
       </c>
       <c r="G10" t="n">
-        <v>0.385</v>
+        <v>-0.1308</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.293</v>
+        <v>0.0605</v>
       </c>
       <c r="I10" t="n">
-        <v>0.678</v>
+        <v>-0.1913</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>0.285</v>
+        <v>-0.2118</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.393</v>
+        <v>0.0605</v>
       </c>
       <c r="O10" t="n">
-        <v>0.678</v>
+        <v>-0.2724</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.8002</v>
+        <v>0.1947</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0006</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2003</v>
+        <v>0.1947</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1225</v>
+        <v>0.5355</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1222</v>
+        <v>0.3036</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0002</v>
+        <v>0.2319</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.2211</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="11">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0771</v>
+        <v>-1.942</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7872</v>
+        <v>-1.6795</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2899</v>
+        <v>-0.2625</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9154</v>
+        <v>-0.9282</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7867</v>
+        <v>-0.7887</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1287</v>
+        <v>-0.1395</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.658</v>
+        <v>-0.644</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.658</v>
+        <v>-0.644</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2574</v>
+        <v>-0.2842</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1287</v>
+        <v>-0.1447</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1287</v>
+        <v>-0.1395</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.8002</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3614</v>
+        <v>-0.2349</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1289</v>
+        <v>-0.0618</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2325</v>
+        <v>-0.1731</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.9713</v>
+        <v>-3.1298</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.8014</v>
+        <v>-2.9344</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1699</v>
+        <v>-0.1954</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.1766</v>
+        <v>-1.266</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4617</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7149</v>
+        <v>-0.7605</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1474</v>
+        <v>0.2588</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1036</v>
+        <v>0.1694</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0438</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.324</v>
+        <v>-1.5248</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5653</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7587</v>
+        <v>-0.8499</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.8008</v>
+        <v>-2.7263</v>
       </c>
       <c r="Q12" t="n">
-        <v>-5.0014</v>
+        <v>-4.8684</v>
       </c>
       <c r="R12" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1937</v>
+        <v>-0.3586</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.3469</v>
+        <v>-0.7669</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1533</v>
+        <v>0.4084</v>
       </c>
       <c r="V12" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="W12" t="n">
-        <v>2.3995</v>
+        <v>2.4421</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="13">
@@ -1423,58 +1423,58 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.8753</v>
+        <v>-4.8314</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.8141</v>
+        <v>-5.6847</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9388</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.5535</v>
+        <v>-4.5577</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.0602</v>
+        <v>-2.0582</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.4934</v>
+        <v>-2.4995</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.9446</v>
+        <v>-2.7803</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.9525</v>
+        <v>-0.8517</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.9921</v>
+        <v>-1.9286</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.6089</v>
+        <v>-1.7775</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.1077</v>
+        <v>-1.2065</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.5013</v>
+        <v>-0.571</v>
       </c>
       <c r="P13" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R13" t="n">
-        <v>2.4007</v>
+        <v>2.3368</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7219</v>
+        <v>-0.6631</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.869</v>
+        <v>-0.9571</v>
       </c>
       <c r="U13" t="n">
-        <v>0.147</v>
+        <v>0.2939</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.912199999999996</v>
+        <v>6.470899999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.6407</v>
+        <v>0.9096000000000037</v>
       </c>
       <c r="F14" t="n">
-        <v>7.552599999999999</v>
+        <v>5.5614</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.609</v>
+        <v>-2.7564</v>
       </c>
       <c r="H14" t="n">
-        <v>-4.0681</v>
+        <v>-3.987099999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>1.458799999999999</v>
+        <v>1.2305</v>
       </c>
       <c r="J14" t="n">
-        <v>3.62</v>
+        <v>4.623800000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>1.0794</v>
+        <v>1.801899999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>2.5406</v>
+        <v>2.822</v>
       </c>
       <c r="M14" t="n">
-        <v>-6.229100000000001</v>
+        <v>-7.3803</v>
       </c>
       <c r="N14" t="n">
-        <v>-5.147499999999999</v>
+        <v>-5.7889</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.0816</v>
+        <v>-1.5916</v>
       </c>
       <c r="P14" t="n">
-        <v>2.0007</v>
+        <v>1.9476</v>
       </c>
       <c r="Q14" t="n">
-        <v>-14.0041</v>
+        <v>-13.6317</v>
       </c>
       <c r="R14" t="n">
-        <v>16.0047</v>
+        <v>15.5788</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6779999999999999</v>
+        <v>-0.04620000000000002</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.633699999999999</v>
+        <v>-3.7424</v>
       </c>
       <c r="U14" t="n">
-        <v>3.955600000000001</v>
+        <v>3.6961</v>
       </c>
       <c r="V14" t="n">
-        <v>7.198600000000001</v>
+        <v>7.3264</v>
       </c>
       <c r="W14" t="n">
-        <v>13.3769</v>
+        <v>13.6595</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.1785</v>
+        <v>-6.333299999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1671</v>
+        <v>2.6375</v>
       </c>
       <c r="E15" t="n">
-        <v>1.56</v>
+        <v>1.1779</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6071</v>
+        <v>1.4595</v>
       </c>
       <c r="G15" t="n">
-        <v>1.2178</v>
+        <v>1.2187</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4068</v>
+        <v>0.3987</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9397</v>
+        <v>0.9647</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9397</v>
+        <v>0.9647</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2781</v>
+        <v>0.254</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1287</v>
+        <v>-0.1447</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4068</v>
+        <v>0.3987</v>
       </c>
       <c r="P15" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S15" t="n">
-        <v>0.949</v>
+        <v>0.4451</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6202</v>
+        <v>0.2132</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3287</v>
+        <v>0.2319</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,31 +1657,31 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7997</v>
+        <v>1.8316</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7997</v>
+        <v>1.8316</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1.7997</v>
+        <v>1.8316</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5998</v>
+        <v>0.6158</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1998</v>
+        <v>1.2158</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7997</v>
+        <v>1.8316</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5998</v>
+        <v>0.6158</v>
       </c>
       <c r="L16" t="n">
-        <v>1.1998</v>
+        <v>1.2158</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6829</v>
+        <v>1.3883</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7052</v>
+        <v>2.458</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0223</v>
+        <v>-1.0697</v>
       </c>
       <c r="G17" t="n">
-        <v>4.738</v>
+        <v>4.7411</v>
       </c>
       <c r="H17" t="n">
-        <v>2.0027</v>
+        <v>1.974</v>
       </c>
       <c r="I17" t="n">
-        <v>2.7352</v>
+        <v>2.7671</v>
       </c>
       <c r="J17" t="n">
-        <v>4.4829</v>
+        <v>4.6147</v>
       </c>
       <c r="K17" t="n">
-        <v>1.3614</v>
+        <v>1.4292</v>
       </c>
       <c r="L17" t="n">
-        <v>3.1215</v>
+        <v>3.1855</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2551</v>
+        <v>0.1265</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6413</v>
+        <v>0.5448</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3862</v>
+        <v>-0.4184</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.2012</v>
+        <v>-4.0895</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7744</v>
+        <v>-0.1329</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8957000000000001</v>
+        <v>-0.4578</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1213</v>
+        <v>0.3249</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2801</v>
+        <v>-1.2726</v>
       </c>
       <c r="W17" t="n">
-        <v>2.3192</v>
+        <v>2.3905</v>
       </c>
       <c r="X17" t="n">
-        <v>-3.5993</v>
+        <v>-3.6632</v>
       </c>
     </row>
     <row r="18">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.673</v>
+        <v>0.761</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3414</v>
+        <v>0.5518</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3316</v>
+        <v>0.2092</v>
       </c>
       <c r="G18" t="n">
-        <v>4.8158</v>
+        <v>4.8172</v>
       </c>
       <c r="H18" t="n">
-        <v>4.0247</v>
+        <v>4.0246</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7911</v>
+        <v>0.7926</v>
       </c>
       <c r="J18" t="n">
-        <v>5.5605</v>
+        <v>5.7118</v>
       </c>
       <c r="K18" t="n">
-        <v>4.1188</v>
+        <v>4.2284</v>
       </c>
       <c r="L18" t="n">
-        <v>1.4417</v>
+        <v>1.4834</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7447</v>
+        <v>-0.8946</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0941</v>
+        <v>-0.2038</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6506</v>
+        <v>-0.6907</v>
       </c>
       <c r="P18" t="n">
-        <v>-3.601</v>
+        <v>-3.5053</v>
       </c>
       <c r="Q18" t="n">
-        <v>-5.0014</v>
+        <v>-4.8684</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6579</v>
+        <v>0.67</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2177</v>
+        <v>-0.2916</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8756</v>
+        <v>0.9617</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="19">
@@ -1891,31 +1891,31 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5903</v>
+        <v>0.2516</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3324</v>
+        <v>0.4989</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2579</v>
+        <v>-0.2473</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.6011</v>
+        <v>-1.5238</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3704</v>
+        <v>0.4244</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.9715</v>
+        <v>-1.9482</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.1069</v>
+        <v>-0.9252</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2072</v>
+        <v>0.3388</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3141</v>
+        <v>-1.264</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4942</v>
+        <v>-0.5986</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1633</v>
+        <v>0.0856</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6574</v>
+        <v>-0.6842</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2514</v>
+        <v>0.8339</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0401</v>
+        <v>-0.0443</v>
       </c>
       <c r="U20" t="n">
-        <v>1.2113</v>
+        <v>0.8781</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9416</v>
       </c>
       <c r="W20" t="n">
-        <v>2.3995</v>
+        <v>2.4421</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="21">
@@ -2047,40 +2047,40 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0911</v>
+        <v>0.0916</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0445</v>
+        <v>-0.0413</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1556</v>
+        <v>0.1534</v>
       </c>
       <c r="H21" t="n">
-        <v>0.02</v>
+        <v>0.0205</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="J21" t="n">
-        <v>0.02</v>
+        <v>0.0205</v>
       </c>
       <c r="K21" t="n">
-        <v>0.02</v>
+        <v>0.0205</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2092,10 +2092,10 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0645</v>
+        <v>-0.0618</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0645</v>
+        <v>-0.0618</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5502</v>
+        <v>-0.5622</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7655</v>
+        <v>-1.1245</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2153</v>
+        <v>0.5623</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4473</v>
+        <v>-0.5629999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>0.012</v>
+        <v>-0.057</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4594</v>
+        <v>-0.506</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4835</v>
+        <v>0.5552</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1636</v>
+        <v>0.231</v>
       </c>
       <c r="L22" t="n">
-        <v>0.32</v>
+        <v>0.3242</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-1.1182</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1515</v>
+        <v>-0.288</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7793</v>
+        <v>-0.8302</v>
       </c>
       <c r="P22" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R22" t="n">
-        <v>2.6007</v>
+        <v>2.5316</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0437</v>
+        <v>0.1382</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0487</v>
+        <v>-0.5113</v>
       </c>
       <c r="U22" t="n">
-        <v>0.005</v>
+        <v>0.6495</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="23">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.1409</v>
+        <v>-1.1863</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.4124</v>
+        <v>-1.2054</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2715</v>
+        <v>0.0191</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.8184</v>
+        <v>-1.7775</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7892</v>
+        <v>-0.7661</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.0292</v>
+        <v>-1.0114</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.0324</v>
+        <v>-0.9433</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3963</v>
+        <v>-0.3437</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6361</v>
+        <v>-0.5995</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.7861</v>
+        <v>-0.8342000000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.393</v>
+        <v>-0.4224</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3931</v>
+        <v>-0.4118</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2774</v>
+        <v>0.2017</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3801</v>
+        <v>-0.2621</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6575</v>
+        <v>0.4638</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.6933</v>
+        <v>-1.3021</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.8307</v>
+        <v>-2.3994</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1374</v>
+        <v>1.0974</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.5527</v>
+        <v>-1.451</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.7554</v>
+        <v>-0.7692</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.7972</v>
+        <v>-0.6818</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.3228</v>
+        <v>-1.1248</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.3763</v>
+        <v>-0.3232</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.9465</v>
+        <v>-0.8015</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.2298</v>
+        <v>-0.3262</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.3791</v>
+        <v>-0.446</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1493</v>
+        <v>0.1198</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.4001</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6002</v>
+        <v>-0.3516</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7668</v>
+        <v>-0.6331</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1666</v>
+        <v>0.2815</v>
       </c>
       <c r="V24" t="n">
-        <v>0.8597</v>
+        <v>0.89</v>
       </c>
       <c r="W24" t="n">
-        <v>1.4596</v>
+        <v>1.5005</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.5999</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.2444</v>
+        <v>-1.9489</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.9231</v>
+        <v>-2.2516</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6787</v>
+        <v>0.3027</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.1778</v>
+        <v>-1.1871</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.0841</v>
+        <v>-1.1192</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.09370000000000001</v>
+        <v>-0.0679</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.2469</v>
+        <v>-0.0689</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.9325</v>
+        <v>-0.8312</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6856</v>
+        <v>0.7623</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-1.1182</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.1515</v>
+        <v>-0.288</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.7793</v>
+        <v>-0.8302</v>
       </c>
       <c r="P25" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R25" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4073</v>
+        <v>-0.0401</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.4758</v>
+        <v>-1.0143</v>
       </c>
       <c r="U25" t="n">
-        <v>1.0685</v>
+        <v>0.9741</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.8873</v>
+        <v>-7.7582</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.9152</v>
+        <v>-5.6654</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.9721</v>
+        <v>-2.0928</v>
       </c>
       <c r="G26" t="n">
-        <v>-4.1204</v>
+        <v>-4.1112</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.144</v>
+        <v>-1.1808</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.9763</v>
+        <v>-2.9304</v>
       </c>
       <c r="J26" t="n">
-        <v>-3.948</v>
+        <v>-3.8639</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.5413</v>
       </c>
       <c r="L26" t="n">
-        <v>-3.39</v>
+        <v>-3.3225</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.1723</v>
+        <v>-0.2473</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.586</v>
+        <v>-0.6394</v>
       </c>
       <c r="O26" t="n">
-        <v>0.4137</v>
+        <v>0.3921</v>
       </c>
       <c r="P26" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R26" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.5677</v>
+        <v>-0.3733</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.7668</v>
+        <v>-0.6331</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1991</v>
+        <v>0.2598</v>
       </c>
       <c r="V26" t="n">
-        <v>-3.5993</v>
+        <v>-3.6632</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-3.5993</v>
+        <v>-3.6632</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.912100000000001</v>
+        <v>-5.188200000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>-7.5528</v>
+        <v>-5.5615</v>
       </c>
       <c r="F27" t="n">
-        <v>1.6407</v>
+        <v>0.3733</v>
       </c>
       <c r="G27" t="n">
-        <v>2.609100000000002</v>
+        <v>2.756299999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>4.0679</v>
+        <v>3.987000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.4589</v>
+        <v>-1.230699999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>6.229199999999999</v>
+        <v>7.380299999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>5.1474</v>
+        <v>5.789</v>
       </c>
       <c r="L27" t="n">
-        <v>1.0818</v>
+        <v>1.591600000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>-3.620099999999999</v>
+        <v>-4.6239</v>
       </c>
       <c r="N27" t="n">
-        <v>-1.0793</v>
+        <v>-1.8019</v>
       </c>
       <c r="O27" t="n">
-        <v>-2.5405</v>
+        <v>-2.822</v>
       </c>
       <c r="P27" t="n">
-        <v>-2.000599999999999</v>
+        <v>-1.9474</v>
       </c>
       <c r="Q27" t="n">
-        <v>-16.0044</v>
+        <v>-15.5789</v>
       </c>
       <c r="R27" t="n">
-        <v>14.004</v>
+        <v>13.6317</v>
       </c>
       <c r="S27" t="n">
-        <v>0.6778999999999998</v>
+        <v>1.3292</v>
       </c>
       <c r="T27" t="n">
-        <v>-3.9558</v>
+        <v>-3.6962</v>
       </c>
       <c r="U27" t="n">
-        <v>4.633599999999999</v>
+        <v>5.0253</v>
       </c>
       <c r="V27" t="n">
-        <v>-7.1987</v>
+        <v>-7.3263</v>
       </c>
       <c r="W27" t="n">
-        <v>6.1783</v>
+        <v>6.333099999999999</v>
       </c>
       <c r="X27" t="n">
-        <v>-13.3771</v>
+        <v>-13.6595</v>
       </c>
     </row>
   </sheetData>
